--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/朱远亮_脚本与截图/软件测试测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/朱远亮_脚本与截图/软件测试测试用例.xlsx
@@ -11,7 +11,7 @@
     <sheet name="用例统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$M$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$M$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>注册_账号密码正确</t>
+          <t>注册_正常</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/register userAccount=Zyl_New01 userPassword=12345678 checkPassword=12345678</t>
+          <t>POST /user/register userAccount=Zyl_New01 userPassword=12345678 checkPassword=12345678</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, userId&gt;0</t>
+          <t>code=0, userId&gt;0</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -631,17 +631,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>TC_New01 已存在</t>
+          <t>TC-New01 已存在</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>1. 重复 TC-UR-001</t>
+          <t>重复注册</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 提示账号重复</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
@@ -684,17 +684,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1. userPassword=12345678 checkPassword=87654321</t>
+          <t>userPassword!=checkPassword</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -709,7 +709,7 @@
     <row r="5" ht="80" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-004</t>
+          <t>TC-UL-001</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/用户登录</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -728,26 +728,26 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>注册_账号为空</t>
+          <t>登录_正常</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>testuser01 已存在</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount=''</t>
+          <t>POST /user/login userAccount=testuser01 userPassword=12345678</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0, Set-Cookie</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -762,7 +762,7 @@
     <row r="6" ht="80" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-005</t>
+          <t>TC-UL-002</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/用户登录</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -781,26 +781,26 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>注册_账号长度不足4</t>
+          <t>登录_密码错误</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount='abc'(3字符)</t>
+          <t>wrongPassword</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 提示账号长度不足</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -815,7 +815,7 @@
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-001</t>
+          <t>TC-UL-003</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -838,22 +838,22 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>登录_账号密码正确</t>
+          <t>登录_账号不存在</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/login userAccount=testuser01 userPassword=12345678</t>
+          <t>userAccount=notexist</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, Set-Cookie 含登录态</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -868,7 +868,7 @@
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-002</t>
+          <t>TC-GC-001</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/获取当前用户</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -891,22 +891,22 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>登录_密码错误</t>
+          <t>获取_已登录</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>已登录 Cookie</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1. password=wrongpass</t>
+          <t>GET /user/get/login</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0, 用户信息</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -921,7 +921,7 @@
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-003</t>
+          <t>TC-GC-002</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/获取当前用户</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -940,26 +940,26 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>登录_账号不存在</t>
+          <t>获取_未登录</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>无 Cookie</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount=testuser99</t>
+          <t>GET /user/get/login</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -974,7 +974,7 @@
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-004</t>
+          <t>TC-UM-001</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/更新我的信息</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -993,26 +993,26 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>登录_账号密码都为空</t>
+          <t>更新_正常昵称</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>已登录</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1. 空 body</t>
+          <t>POST /user/update/my userName='新名'</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
     <row r="11" ht="80" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-005</t>
+          <t>TC-UM-002</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/更新我的信息</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1046,26 +1046,26 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>登录_密码小于8字符</t>
+          <t>更新_昵称为空</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>已登录</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1. password='1234567'</t>
+          <t>userName=''</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1080,7 +1080,7 @@
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-UM-003</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1090,36 +1090,35 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/更新我的信息</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>性能测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>登录_50并发</t>
+          <t>更新_未登录</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 50 线程 5s 内启动
-2. POST /user/login 正确账号密码</t>
+          <t>POST /user/update/my</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 500ms, 错误率 &lt; 1%</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1134,7 +1133,7 @@
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-API-001</t>
+          <t>TC-UA-001</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1144,36 +1143,35 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员新增用户</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>注册_Content-Type错误</t>
+          <t>新增_正常</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>admin 已登录</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1. Content-Type=application/xml
-2. POST /user/register body=XML</t>
+          <t>POST /user/add userAccount=Zyl_Admin01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>返回 415</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1188,7 +1186,7 @@
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-UA-002</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1198,12 +1196,12 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员新增用户</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E14" s="3" t="n">
@@ -1211,23 +1209,22 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>登录_SQL注入</t>
+          <t>新增_普通用户越权</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1. password = "' OR 1=1 --"
-2. POST /user/login</t>
+          <t>POST /user/add</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 拒绝登录</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1242,7 +1239,7 @@
     <row r="15" ht="80" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-006</t>
+          <t>TC-UA-003</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1252,7 +1249,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员新增用户</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1261,26 +1258,26 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>注册_账号长度边界20</t>
+          <t>新增_未登录</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount=20字符</t>
+          <t>POST /user/add</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>返回code=0</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1295,7 +1292,7 @@
     <row r="16" ht="80" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-007</t>
+          <t>TC-UG-001</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1305,7 +1302,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员获取用户</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1314,26 +1311,26 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>注册_账号含特殊字符</t>
+          <t>按id获取_正常</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount='test@user.cn'</t>
+          <t>GET /user/get?id=1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0, 用户信息</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1348,7 +1345,7 @@
     <row r="17" ht="80" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-008</t>
+          <t>TC-UG-002</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1358,7 +1355,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员获取用户</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -1367,26 +1364,26 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>注册_纯数字账号</t>
+          <t>按id获取_不存在</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount='123456'</t>
+          <t>GET /user/get?id=999999</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001 纯数字不允许</t>
+          <t>code=40001</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1401,7 +1398,7 @@
     <row r="18" ht="80" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-009</t>
+          <t>TC-UV-001</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1411,7 +1408,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员获取VO</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -1420,26 +1417,26 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>注册_密码含中文</t>
+          <t>获取VO_正常</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1. userPassword='密码12345678'</t>
+          <t>GET /user/get/vo?id=1</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1454,7 +1451,7 @@
     <row r="19" ht="80" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-UR-010</t>
+          <t>TC-UV-002</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1464,7 +1461,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/管理员获取VO</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1473,26 +1470,26 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>注册_账号含emoji</t>
+          <t>获取VO_普通用户越权</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1. userAccount='test😀01'</t>
+          <t>GET /user/get/vo?id=1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1507,7 +1504,7 @@
     <row r="20" ht="80" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-006</t>
+          <t>TC-UD-001</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1517,7 +1514,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员删除用户</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1530,24 +1527,22 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>登录_退出后Cookie失效</t>
+          <t>删除_正常</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1. 先登录拿Cookie
-2. POST /user/logout
-3. 用旧Cookie访问 /user/get/login</t>
+          <t>POST /user/delete id=新用户id</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>返回code=40100</t>
+          <t>code=0, isDelete=1</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1562,7 +1557,7 @@
     <row r="21" ht="80" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-007</t>
+          <t>TC-UD-002</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1572,7 +1567,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员删除用户</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1581,26 +1576,26 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>登录_连续5次密码错</t>
+          <t>删除_普通用户越权</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1. 连续5次错误密码</t>
+          <t>POST /user/delete</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>返回5次code=40001</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1615,7 +1610,7 @@
     <row r="22" ht="80" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-008</t>
+          <t>TC-UU-001</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1625,36 +1620,35 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员更新用户</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>登录_缺Content-Type</t>
+          <t>更新_正常昵称</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1. 不设置Content-Type
-2. POST /user/login</t>
+          <t>POST /user/update id=新id userName='改名'</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>返回415或服务端解析</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1669,7 +1663,7 @@
     <row r="23" ht="80" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-009</t>
+          <t>TC-UU-002</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1679,7 +1673,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员更新用户</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1688,26 +1682,26 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>登录_密码仅大小写不同</t>
+          <t>更新_普通用户越权</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1. password='12345678A' (实际是小写)</t>
+          <t>POST /user/update</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -1722,7 +1716,7 @@
     <row r="24" ht="80" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-010</t>
+          <t>TC-LP-001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1732,7 +1726,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>/用户登录</t>
+          <t>/管理员分页查询</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1741,26 +1735,26 @@
         </is>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>登录_密码含空格</t>
+          <t>分页查询_正常</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1. password=' 12345678 '</t>
+          <t>POST /user/list/page/vo current=1 pageSize=10</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>code=0, records列表</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1775,7 +1769,7 @@
     <row r="25" ht="80" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-UA-001</t>
+          <t>TC-LP-002</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1785,7 +1779,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>/用户管理</t>
+          <t>/管理员分页查询</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -1794,26 +1788,26 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>管理员查询用户列表</t>
+          <t>分页查询_普通用户越权</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/list/page/vo current=1 pageSize=10</t>
+          <t>POST /user/list/page/vo</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>返回code=0, records含用户列表</t>
+          <t>code=40300</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
@@ -1828,7 +1822,7 @@
     <row r="26" ht="80" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-UA-002</t>
+          <t>TC-LO-001</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1838,7 +1832,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>/用户管理</t>
+          <t>/用户注销</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
@@ -1847,26 +1841,26 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>管理员按昵称搜索</t>
+          <t>注销_正常</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>已登录</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/list/page/vo userName='test'</t>
+          <t>POST /user/logout</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>返回code=0 含test的记录</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
@@ -1881,7 +1875,7 @@
     <row r="27" ht="80" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TC-UA-003</t>
+          <t>TC-LO-002</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1891,12 +1885,12 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>/用户管理</t>
+          <t>/用户注销</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E27" s="3" t="n">
@@ -1904,22 +1898,22 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>普通用户越权调用</t>
+          <t>注销_未登录</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1. POST /user/list/page/vo</t>
+          <t>POST /user/logout</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>返回code=40300</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -1934,7 +1928,7 @@
     <row r="28" ht="80" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-002</t>
+          <t>TC-PERF-001</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1944,7 +1938,7 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>/用户注册</t>
+          <t>/用户登录</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
@@ -1957,23 +1951,22 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>注册_20并发</t>
+          <t>登录_50并发</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>已安装 JMeter</t>
+          <t>JMeter</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1. JMeter 20 线程 5s 内启动
-2. POST /user/register</t>
+          <t>50线程 POST /user/login</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>P95 &lt; 800ms, 错误率 &lt; 1%</t>
+          <t>P95&lt;500ms</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -1988,7 +1981,7 @@
     <row r="29" ht="80" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC-API-002</t>
+          <t>TC-API-001</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2011,22 +2004,22 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>注册_缺userAccount字段</t>
+          <t>注册_Content-Type错误</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1. body 只有 userPassword 和 checkPassword</t>
+          <t>Content-Type=application/xml</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>返回code=40001</t>
+          <t>415</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -2038,8 +2031,114 @@
       </c>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
+    <row r="30" ht="80" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-001</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>/用户登录</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>安全测试</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>SQL注入_登录</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>password="' OR 1=1 --"</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>code=40001</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>朱远亮</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31" ht="80" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TC-SEC-002</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>内娱图库StarPicture</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>/管理员</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>安全测试</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>越权_普通用户改userRole</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>testuser01</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>POST /user/update role='admin'</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>code=40300</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>朱远亮</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M29"/>
+  <autoFilter ref="A1:M31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2076,17 +2175,17 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>接口测试</t>
+          <t>安全测试</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -2096,17 +2195,17 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>安全测试</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -2116,7 +2215,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/朱远亮_脚本与截图/软件测试测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/朱远亮_脚本与截图/软件测试测试用例.xlsx
@@ -8,11 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="用例统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试用例'!$A$1:$M$31</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -20,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,14 +28,7 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -50,7 +40,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,39 +54,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="00999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="00999999"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00999999"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -462,25 +436,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>用例编号</t>
@@ -547,7 +521,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="80" customHeight="1">
+    <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>TC-UR-001</t>
@@ -555,40 +529,41 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>/用户注册</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>/user/register</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>注册_正常</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>无账号</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>POST /user/register userAccount=Zyl_New01 userPassword=12345678 checkPassword=12345678</t>
+          <t>POST /user/register
+Body: userAccount=newtest, userPassword=Test12345, checkPassword=Test12345</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>code=0, userId&gt;0</t>
+          <t>code=0, data 含 userId</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -600,7 +575,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr"/>
     </row>
-    <row r="3" ht="80" customHeight="1">
+    <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>TC-UR-002</t>
@@ -608,40 +583,41 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>/用户注册</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>/user/register</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>注册_账号已存在</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>TC-New01 已存在</t>
+          <t>newtest 已注册</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>重复注册</t>
+          <t>POST /user/register
+Body: userAccount=newtest, userPassword=Test12345, checkPassword=Test12345</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=40001, 提示账号已存在</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -653,7 +629,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr"/>
     </row>
-    <row r="4" ht="80" customHeight="1">
+    <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TC-UR-003</t>
@@ -661,25 +637,25 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>/用户注册</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>注册_密码不一致</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>/user/register</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>注册_账号为空</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -689,12 +665,13 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>userPassword!=checkPassword</t>
+          <t>POST /user/register
+Body: userAccount=, userPassword=Test12345, checkPassword=Test12345</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=40001, 提示账号不能为空</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
@@ -706,48 +683,49 @@
       </c>
       <c r="M4" s="2" t="inlineStr"/>
     </row>
-    <row r="5" ht="80" customHeight="1">
+    <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-001</t>
+          <t>TC-UR-004</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>/用户登录</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>登录_正常</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>/user/register</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>注册_密码不一致</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>testuser01 已存在</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>POST /user/login userAccount=testuser01 userPassword=12345678</t>
+          <t>POST /user/register
+Body: userAccount=test01, userPassword=Test12345, checkPassword=Test11111</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>code=0, Set-Cookie</t>
+          <t>code=40001, 提示密码不一致</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -759,48 +737,49 @@
       </c>
       <c r="M5" s="2" t="inlineStr"/>
     </row>
-    <row r="6" ht="80" customHeight="1">
+    <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-002</t>
+          <t>TC-UR-005</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>/用户登录</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>登录_密码错误</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>/user/register</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>注册_账号长度不足4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>wrongPassword</t>
+          <t>POST /user/register
+Body: userAccount=abc, userPassword=Test12345, checkPassword=Test12345</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=40001, 提示账号长度不足</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -812,48 +791,49 @@
       </c>
       <c r="M6" s="2" t="inlineStr"/>
     </row>
-    <row r="7" ht="80" customHeight="1">
+    <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TC-UL-003</t>
+          <t>TC-UL-001</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>/用户登录</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>/user/login</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>登录_账号不存在</t>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>登录_正常</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01 已存在</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>userAccount=notexist</t>
+          <t>POST /user/login
+Body: userAccount=testuser01, userPassword=12345678</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=0, Set-Cookie, data 含 userInfo</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -865,48 +845,49 @@
       </c>
       <c r="M7" s="2" t="inlineStr"/>
     </row>
-    <row r="8" ht="80" customHeight="1">
+    <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-001</t>
+          <t>TC-UL-002</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>/获取当前用户</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>/user/login</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>获取_已登录</t>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>登录_密码错误</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>已登录 Cookie</t>
+          <t>testuser01 已存在</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>GET /user/get/login</t>
+          <t>POST /user/login
+Body: userAccount=testuser01, userPassword=wrongpass</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>code=0, 用户信息</t>
+          <t>code=40001, 提示密码错误</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -918,48 +899,49 @@
       </c>
       <c r="M8" s="2" t="inlineStr"/>
     </row>
-    <row r="9" ht="80" customHeight="1">
+    <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TC-GC-002</t>
+          <t>TC-UL-003</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>/获取当前用户</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>获取_未登录</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>/user/login</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>登录_账号不存在</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>无 Cookie</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>GET /user/get/login</t>
+          <t>POST /user/login
+Body: userAccount=nonexist, userPassword=12345678</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>code=40100</t>
+          <t>code=40001, 提示账号不存在</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
@@ -971,48 +953,49 @@
       </c>
       <c r="M9" s="2" t="inlineStr"/>
     </row>
-    <row r="10" ht="80" customHeight="1">
+    <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TC-UM-001</t>
+          <t>TC-UL-004</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>/更新我的信息</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>/user/login</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>更新_正常昵称</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>登录_SQL注入</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>已登录</t>
+          <t>testuser01 已存在</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>POST /user/update/my userName='新名'</t>
+          <t>POST /user/login
+Body: userAccount=testuser01' OR '1'='1, userPassword=12345678</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=40001, 拒绝登录</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
@@ -1024,48 +1007,49 @@
       </c>
       <c r="M10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="80" customHeight="1">
+    <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TC-UM-002</t>
+          <t>TC-UL-005</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>/更新我的信息</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>更新_昵称为空</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>/user/login</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>登录_账号为空</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>已登录</t>
+          <t>无</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>userName=''</t>
+          <t>POST /user/login
+Body: userAccount=, userPassword=12345678</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=40001, 提示账号不能为空</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1077,33 +1061,33 @@
       </c>
       <c r="M11" s="2" t="inlineStr"/>
     </row>
-    <row r="12" ht="80" customHeight="1">
+    <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TC-UM-003</t>
+          <t>TC-UL-006</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>/更新我的信息</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>更新_未登录</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>/user/login</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>登录_密码为空</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1113,12 +1097,13 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>POST /user/update/my</t>
+          <t>POST /user/login
+Body: userAccount=testuser01, userPassword=</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>code=40100</t>
+          <t>code=40001, 提示密码不能为空</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
@@ -1130,48 +1115,49 @@
       </c>
       <c r="M12" s="2" t="inlineStr"/>
     </row>
-    <row r="13" ht="80" customHeight="1">
+    <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TC-UA-001</t>
+          <t>TC-GC-001</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>/管理员新增用户</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>/user/get/login</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>新增_正常</t>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>获取当前登录用户_已登录</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>admin 已登录</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>POST /user/add userAccount=Zyl_Admin01</t>
+          <t>GET /user/get/login
+Cookie: xxx</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=0, data 含 id, userAccount, userName</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
@@ -1183,48 +1169,48 @@
       </c>
       <c r="M13" s="2" t="inlineStr"/>
     </row>
-    <row r="14" ht="80" customHeight="1">
+    <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TC-UA-002</t>
+          <t>TC-GC-002</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>/管理员新增用户</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>/user/get/login</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>新增_普通用户越权</t>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>获取当前登录用户_未登录</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>无 Cookie</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>POST /user/add</t>
+          <t>GET /user/get/login</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>code=40300</t>
+          <t>code=40100, 未登录</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
@@ -1236,48 +1222,49 @@
       </c>
       <c r="M14" s="2" t="inlineStr"/>
     </row>
-    <row r="15" ht="80" customHeight="1">
+    <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TC-UA-003</t>
+          <t>TC-GC-003</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>/管理员新增用户</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>/user/get/login</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>新增_未登录</t>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>获取当前用户_伪造Cookie</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>伪造的 Cookie</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>POST /user/add</t>
+          <t>GET /user/get/login
+Cookie: jwt=xxx伪造的xxx</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>code=40100</t>
+          <t>code=40100, 未登录</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
@@ -1289,48 +1276,49 @@
       </c>
       <c r="M15" s="2" t="inlineStr"/>
     </row>
-    <row r="16" ht="80" customHeight="1">
+    <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TC-UG-001</t>
+          <t>TC-UM-001</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>/管理员获取用户</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>/user/update/my</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>按id获取_正常</t>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>修改个人信息_正常</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>GET /user/get?id=1</t>
+          <t>POST /user/update/my
+Body: userName=新昵称, userProfile=新简介</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>code=0, 用户信息</t>
+          <t>code=0, data 含更新后的信息</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1342,48 +1330,49 @@
       </c>
       <c r="M16" s="2" t="inlineStr"/>
     </row>
-    <row r="17" ht="80" customHeight="1">
+    <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TC-UG-002</t>
+          <t>TC-UM-002</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>/管理员获取用户</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>按id获取_不存在</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>/user/update/my</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>修改个人信息_未登录</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>无 Cookie</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>GET /user/get?id=999999</t>
+          <t>POST /user/update/my
+Body: userName=新昵称</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
@@ -1395,48 +1384,49 @@
       </c>
       <c r="M17" s="2" t="inlineStr"/>
     </row>
-    <row r="18" ht="80" customHeight="1">
+    <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TC-UV-001</t>
+          <t>TC-UM-003</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>/管理员获取VO</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>/user/update/my</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>获取VO_正常</t>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>修改个人信息_XSS</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>GET /user/get/vo?id=1</t>
+          <t>POST /user/update/my
+Body: userName=&lt;script&gt;alert(1)&lt;/script&gt;</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=40001 或 userName 被过滤</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
@@ -1448,48 +1438,49 @@
       </c>
       <c r="M18" s="2" t="inlineStr"/>
     </row>
-    <row r="19" ht="80" customHeight="1">
+    <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TC-UV-002</t>
+          <t>TC-UA-001</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>/管理员获取VO</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>/user/add</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>获取VO_普通用户越权</t>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>管理员新增用户</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>GET /user/get/vo?id=1</t>
+          <t>POST /user/add
+Body: userAccount=newbyadmin, userPassword=Test12345</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>code=40300</t>
+          <t>code=0, data 含 userId</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1501,48 +1492,49 @@
       </c>
       <c r="M19" s="2" t="inlineStr"/>
     </row>
-    <row r="20" ht="80" customHeight="1">
+    <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TC-UD-001</t>
+          <t>TC-UA-002</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>/管理员删除用户</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>/user/add</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>删除_正常</t>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>新增用户_普通用户越权</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>POST /user/delete id=新用户id</t>
+          <t>POST /user/add
+Body: userAccount=xxx, userPassword=Test12345</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>code=0, isDelete=1</t>
+          <t>code=40300, 无权限</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -1554,48 +1546,48 @@
       </c>
       <c r="M20" s="2" t="inlineStr"/>
     </row>
-    <row r="21" ht="80" customHeight="1">
+    <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TC-UD-002</t>
+          <t>TC-UG-001</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>/管理员删除用户</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>/user/get</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>删除_普通用户越权</t>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>按ID查询用户</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>POST /user/delete</t>
+          <t>GET /user/get?id=1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>code=40300</t>
+          <t>code=0, data 含 id=1 的用户信息</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
@@ -1607,48 +1599,48 @@
       </c>
       <c r="M21" s="2" t="inlineStr"/>
     </row>
-    <row r="22" ht="80" customHeight="1">
+    <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TC-UU-001</t>
+          <t>TC-UG-002</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>/管理员更新用户</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>更新_正常昵称</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>/user/get</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>按ID查询_用户不存在</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>POST /user/update id=新id userName='改名'</t>
+          <t>GET /user/get?id=99999</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>code=0</t>
+          <t>code=40001, 用户不存在</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
@@ -1660,48 +1652,48 @@
       </c>
       <c r="M22" s="2" t="inlineStr"/>
     </row>
-    <row r="23" ht="80" customHeight="1">
+    <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TC-UU-002</t>
+          <t>TC-UGV-001</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>/管理员更新用户</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>/user/get/vo</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>更新_普通用户越权</t>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>按ID查询用户VO</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>POST /user/update</t>
+          <t>GET /user/get/vo?id=1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>code=40300</t>
+          <t>code=0, data 含 UserVO</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
@@ -1713,48 +1705,49 @@
       </c>
       <c r="M23" s="2" t="inlineStr"/>
     </row>
-    <row r="24" ht="80" customHeight="1">
+    <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TC-LP-001</t>
+          <t>TC-UD-001</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>/管理员分页查询</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>/user/delete</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>分页查询_正常</t>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>删除用户_正常</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>POST /user/list/page/vo current=1 pageSize=10</t>
+          <t>POST /user/delete
+Body: id=99</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>code=0, records列表</t>
+          <t>code=0</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -1766,43 +1759,44 @@
       </c>
       <c r="M24" s="2" t="inlineStr"/>
     </row>
-    <row r="25" ht="80" customHeight="1">
+    <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TC-LP-002</t>
+          <t>TC-UD-002</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>/管理员分页查询</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>/user/delete</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>分页查询_普通用户越权</t>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>删除用户_普通用户越权</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>POST /user/list/page/vo</t>
+          <t>POST /user/delete
+Body: id=2</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1819,43 +1813,44 @@
       </c>
       <c r="M25" s="2" t="inlineStr"/>
     </row>
-    <row r="26" ht="80" customHeight="1">
+    <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TC-LO-001</t>
+          <t>TC-UU-001</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>/用户注销</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>/user/update</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>注销_正常</t>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>管理员更新用户</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>已登录</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>POST /user/logout</t>
+          <t>POST /user/update
+Body: id=2, userName=updated</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1872,48 +1867,49 @@
       </c>
       <c r="M26" s="2" t="inlineStr"/>
     </row>
-    <row r="27" ht="80" customHeight="1">
+    <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TC-LO-002</t>
+          <t>TC-ULP-001</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>/用户注销</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>/user/list/page/vo</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>注销_未登录</t>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>分页查询用户</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>POST /user/logout</t>
+          <t>POST /user/list/page/vo
+Body: current=1, pageSize=10</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>code=40100</t>
+          <t>code=0, records 有数据</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
@@ -1925,48 +1921,49 @@
       </c>
       <c r="M27" s="2" t="inlineStr"/>
     </row>
-    <row r="28" ht="80" customHeight="1">
+    <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TC-PERF-001</t>
+          <t>TC-ULP-002</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>/用户登录</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>性能测试</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="n">
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>/user/list/page/vo</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>登录_50并发</t>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>分页查询_第0页</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>JMeter</t>
+          <t>admin Cookie</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>50线程 POST /user/login</t>
+          <t>POST /user/list/page/vo
+Body: current=0, pageSize=10</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>P95&lt;500ms</t>
+          <t>code=40001 或返回第1页</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
@@ -1978,48 +1975,48 @@
       </c>
       <c r="M28" s="2" t="inlineStr"/>
     </row>
-    <row r="29" ht="80" customHeight="1">
+    <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TC-API-001</t>
+          <t>TC-ULO-001</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>/用户注册</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>接口测试</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>注册_Content-Type错误</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>/user/logout</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>用户注销</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>testuser01 Cookie</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Content-Type=application/xml</t>
+          <t>POST /user/logout</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>code=0, Cookie 被清除</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
@@ -2031,48 +2028,48 @@
       </c>
       <c r="M29" s="2" t="inlineStr"/>
     </row>
-    <row r="30" ht="80" customHeight="1">
+    <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-001</t>
+          <t>TC-ULO-002</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>/用户登录</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>SQL注入_登录</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>/user/logout</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>注销_未登录</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>无 Cookie</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>password="' OR 1=1 --"</t>
+          <t>POST /user/logout</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>code=40001</t>
+          <t>code=40100</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
@@ -2084,48 +2081,49 @@
       </c>
       <c r="M30" s="2" t="inlineStr"/>
     </row>
-    <row r="31" ht="80" customHeight="1">
+    <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TC-SEC-002</t>
+          <t>TC-PERF-001</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>内娱图库StarPicture</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>/管理员</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>越权_普通用户改userRole</t>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>/user/login</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>登录_50并发</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>testuser01</t>
+          <t>testuser01 已存在</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>POST /user/update role='admin'</t>
+          <t>POST /user/login 50并发
+Body: userAccount=testuser01, userPassword=12345678</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>code=40300</t>
+          <t>P95 &lt; 500ms, 错误率 &lt; 5%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
@@ -2137,86 +2135,60 @@
       </c>
       <c r="M31" s="2" t="inlineStr"/>
     </row>
-  </sheetData>
-  <autoFilter ref="A1:M31"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>测试类型</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>用例数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>功能测试</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>安全测试</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TC-API-001</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>StarPicture</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>/user/register</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>功能测试</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>性能测试</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>接口测试</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>合计</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>30</v>
-      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>注册_Content-Type错误</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>POST /user/register
+Header: Content-Type: application/xml
+Body: &lt;xml&gt;test&lt;/xml&gt;</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>code=40001 或 415</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>朱远亮</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/朱远亮_脚本与截图/软件测试测试用例.xlsx
+++ b/docs/内娱图库_海蒂与爷爷_朱远亮_18144610287/朱远亮_脚本与截图/软件测试测试用例.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>/user/register</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>/user/register</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>/user/register</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>/user/register</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>/user/register</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>/user/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>/user/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>/user/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>/user/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>/user/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>/user/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>/user/get/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>/user/get/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>/user/get/login</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>/user/update/my</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>/user/update/my</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>/user/update/my</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>/user/add</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>/user/add</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>/user/get</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>/user/get</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>/user/get/vo</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>/user/delete</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>/user/delete</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>/user/update</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>/user/list/page/vo</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>/user/list/page/vo</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>/user/logout</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>/user/logout</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>/user/login</t>
+          <t>性能测试</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>/user/register</t>
+          <t>接口测试</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
